--- a/Unity/Assets/Config/Excel/StartConfig/Benchmark/StartSceneConfig@s.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Benchmark/StartSceneConfig@s.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Project\SJET\Unity\Assets\Config\Excel\StartConfig\Benchmark\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ET\ET8X\LockStep\ET\Unity\Assets\Config\Excel\StartConfig\Localhost\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87735C6F-5140-4A3D-97BF-CD17435ECA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8BE1BA-6DA2-424A-B21B-97281A1D8DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
+    <sheet name="Router" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="28">
   <si>
     <t>Id</t>
   </si>
@@ -61,62 +62,57 @@
     <t>string</t>
   </si>
   <si>
-    <t>BenchmarkServer</t>
-  </si>
-  <si>
-    <t>BenchmarkClient</t>
-  </si>
-  <si>
-    <t>BenchmarkClient1</t>
-  </si>
-  <si>
-    <t>BenchmarkClient2</t>
-  </si>
-  <si>
-    <t>BenchmarkClient3</t>
-  </si>
-  <si>
-    <t>BenchmarkClient4</t>
-  </si>
-  <si>
-    <t>BenchmarkClient5</t>
-  </si>
-  <si>
-    <t>BenchmarkClient6</t>
-  </si>
-  <si>
-    <t>BenchmarkClient7</t>
-  </si>
-  <si>
-    <t>BenchmarkClient8</t>
-  </si>
-  <si>
-    <t>BenchmarkClient9</t>
-  </si>
-  <si>
-    <t>BenchmarkClient10</t>
-  </si>
-  <si>
-    <t>BenchmarkClient11</t>
-  </si>
-  <si>
-    <t>BenchmarkClient12</t>
-  </si>
-  <si>
-    <t>BenchmarkClient13</t>
-  </si>
-  <si>
-    <t>BenchmarkClient14</t>
-  </si>
-  <si>
-    <t>BenchmarkClient15</t>
+    <t>Realm</t>
+  </si>
+  <si>
+    <t>Gate</t>
+  </si>
+  <si>
+    <t>Gate1</t>
+  </si>
+  <si>
+    <t>Gate2</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Match</t>
+  </si>
+  <si>
+    <t>Map</t>
+  </si>
+  <si>
+    <t>Map1</t>
+  </si>
+  <si>
+    <t>RouterManager</t>
+  </si>
+  <si>
+    <t>Router</t>
+  </si>
+  <si>
+    <t>Router01</t>
+  </si>
+  <si>
+    <t>Router02</t>
+  </si>
+  <si>
+    <t>Router03</t>
+  </si>
+  <si>
+    <t>Router04</t>
+  </si>
+  <si>
+    <t>Map2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +138,13 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -170,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -184,6 +187,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -489,15 +495,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:H36"/>
+  <dimension ref="C3:H12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="5" width="12.625" style="3" customWidth="1"/>
     <col min="6" max="6" width="15.375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="15.125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="13.125" style="3" customWidth="1"/>
+    <col min="7" max="8" width="13.125" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -578,353 +583,300 @@
         <v>13</v>
       </c>
       <c r="H6" s="5">
-        <v>10001</v>
+        <v>30002</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="5">
+        <v>30003</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C8" s="5">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="5">
+        <v>30004</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C9" s="5">
+        <v>4</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C10" s="5">
+        <v>5</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C11" s="5">
+        <v>6</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C12" s="5">
+        <v>7</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="C3:H10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
+    <col min="3" max="5" width="12.625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.375" style="3" customWidth="1"/>
+    <col min="7" max="8" width="13.125" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C6" s="5">
+        <v>300</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="5">
+        <v>30300</v>
       </c>
     </row>
     <row r="7" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C7" s="5">
-        <v>2</v>
+        <v>301</v>
       </c>
       <c r="D7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="5"/>
+        <v>23</v>
+      </c>
+      <c r="H7" s="5">
+        <v>30301</v>
+      </c>
     </row>
     <row r="8" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C8" s="5">
+        <v>302</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5">
         <v>3</v>
       </c>
-      <c r="D8" s="5">
-        <v>3</v>
-      </c>
-      <c r="E8" s="5">
-        <v>1</v>
-      </c>
       <c r="F8" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="H8" s="5">
+        <v>30302</v>
+      </c>
     </row>
     <row r="9" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C9" s="5">
-        <v>4</v>
+        <v>303</v>
       </c>
       <c r="D9" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E9" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="5"/>
+        <v>25</v>
+      </c>
+      <c r="H9" s="5">
+        <v>30303</v>
+      </c>
     </row>
     <row r="10" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C10" s="5">
-        <v>5</v>
+        <v>304</v>
       </c>
       <c r="D10" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E10" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C11" s="5">
-        <v>6</v>
-      </c>
-      <c r="D11" s="5">
-        <v>6</v>
-      </c>
-      <c r="E11" s="5">
-        <v>1</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C12" s="5">
-        <v>7</v>
-      </c>
-      <c r="D12" s="5">
-        <v>7</v>
-      </c>
-      <c r="E12" s="5">
-        <v>1</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C13" s="5">
-        <v>8</v>
-      </c>
-      <c r="D13" s="5">
-        <v>8</v>
-      </c>
-      <c r="E13" s="5">
-        <v>1</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C14" s="5">
-        <v>9</v>
-      </c>
-      <c r="D14" s="5">
-        <v>9</v>
-      </c>
-      <c r="E14" s="5">
-        <v>1</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C15" s="5">
-        <v>10</v>
-      </c>
-      <c r="D15" s="5">
-        <v>10</v>
-      </c>
-      <c r="E15" s="5">
-        <v>1</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C16" s="5">
-        <v>11</v>
-      </c>
-      <c r="D16" s="5">
-        <v>11</v>
-      </c>
-      <c r="E16" s="5">
-        <v>1</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C17" s="5">
-        <v>12</v>
-      </c>
-      <c r="D17" s="5">
-        <v>12</v>
-      </c>
-      <c r="E17" s="5">
-        <v>1</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C18" s="5">
-        <v>13</v>
-      </c>
-      <c r="D18" s="5">
-        <v>13</v>
-      </c>
-      <c r="E18" s="5">
-        <v>1</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C19" s="5">
-        <v>14</v>
-      </c>
-      <c r="D19" s="5">
-        <v>14</v>
-      </c>
-      <c r="E19" s="5">
-        <v>1</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C20" s="5">
-        <v>15</v>
-      </c>
-      <c r="D20" s="5">
-        <v>15</v>
-      </c>
-      <c r="E20" s="5">
-        <v>1</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C21" s="5">
-        <v>16</v>
-      </c>
-      <c r="D21" s="5">
-        <v>16</v>
-      </c>
-      <c r="E21" s="5">
-        <v>1</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="H25" s="5"/>
-    </row>
-    <row r="26" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="H26" s="5"/>
-    </row>
-    <row r="27" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="H27" s="5"/>
-    </row>
-    <row r="28" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="H28" s="5"/>
-    </row>
-    <row r="29" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="H29" s="5"/>
-    </row>
-    <row r="30" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="H30" s="5"/>
-    </row>
-    <row r="31" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="H31" s="5"/>
-    </row>
-    <row r="32" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="H32" s="5"/>
-    </row>
-    <row r="33" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="H33" s="5"/>
-    </row>
-    <row r="34" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="H34" s="5"/>
-    </row>
-    <row r="35" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="H35" s="5"/>
-    </row>
-    <row r="36" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="H36" s="5"/>
+      <c r="H10" s="5">
+        <v>30304</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/Unity/Assets/Config/Excel/StartConfig/Benchmark/StartSceneConfig@s.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Benchmark/StartSceneConfig@s.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\ET\ET8X\LockStep\ET\Unity\Assets\Config\Excel\StartConfig\Localhost\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8BE1BA-6DA2-424A-B21B-97281A1D8DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510B6532-B52B-4EC2-8C04-EB7391106BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2355" yWindow="1380" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="29">
   <si>
     <t>Id</t>
   </si>
@@ -105,6 +105,10 @@
   </si>
   <si>
     <t>Map2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map3</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -495,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:H12"/>
+  <dimension ref="C3:H13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -697,6 +701,24 @@
         <v>27</v>
       </c>
       <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C13" s="5">
+        <v>8</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
